--- a/data/raw/benv_exports/salmonellosi_aviare_non_tifoidee_2026_italia.xlsx
+++ b/data/raw/benv_exports/salmonellosi_aviare_non_tifoidee_2026_italia.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K43"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -414,7 +414,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>84464</v>
+        <v>83780</v>
       </c>
       <c r="B2" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -423,33 +423,33 @@
         <v>E</v>
       </c>
       <c r="D2" t="str">
-        <v>30/04/2026</v>
+        <v>19/03/2026</v>
       </c>
       <c r="E2" t="str">
-        <v>30/04/2026</v>
+        <v>17/03/2026</v>
       </c>
       <c r="F2" t="str">
-        <v>07/07/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="G2" t="str">
-        <v>ENTERITIDIS</v>
+        <v>TYPHIMURIUM MONOFASICA VAR (1,4[5],12:I:-)</v>
       </c>
       <c r="H2" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I2" t="str">
-        <v>DERUTA</v>
+        <v>TUSCANIA</v>
       </c>
       <c r="J2" t="str">
-        <v>PG</v>
+        <v>VT</v>
       </c>
       <c r="K2" t="str">
-        <v>UMBRIA</v>
+        <v>LAZIO</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>84625</v>
+        <v>83997</v>
       </c>
       <c r="B3" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -458,13 +458,13 @@
         <v>E</v>
       </c>
       <c r="D3" t="str">
-        <v>20/05/2026</v>
+        <v>30/03/2026</v>
       </c>
       <c r="E3" t="str">
-        <v>15/05/2026</v>
+        <v>24/03/2026</v>
       </c>
       <c r="F3" t="str">
-        <v>20/05/2026</v>
+        <v>08/04/2026</v>
       </c>
       <c r="G3" t="str">
         <v>KENTUCKY</v>
@@ -473,18 +473,18 @@
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I3" t="str">
-        <v>MATERA</v>
+        <v>MONTE SAN GIOVANNI CAMPANO</v>
       </c>
       <c r="J3" t="str">
-        <v>MT</v>
+        <v>FR</v>
       </c>
       <c r="K3" t="str">
-        <v>BASILICATA</v>
+        <v>LAZIO</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>83784</v>
+        <v>84464</v>
       </c>
       <c r="B4" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -493,33 +493,33 @@
         <v>E</v>
       </c>
       <c r="D4" t="str">
-        <v>13/03/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="E4" t="str">
-        <v>13/03/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="F4" t="str">
-        <v>20/03/2026</v>
+        <v>07/07/2026</v>
       </c>
       <c r="G4" t="str">
-        <v>TYPHIMURIUM</v>
+        <v>ENTERITIDIS</v>
       </c>
       <c r="H4" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I4" t="str">
-        <v>PARMA</v>
+        <v>DERUTA</v>
       </c>
       <c r="J4" t="str">
-        <v>PR</v>
+        <v>PG</v>
       </c>
       <c r="K4" t="str">
-        <v>EMILIA ROMAGNA</v>
+        <v>UMBRIA</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>84719</v>
+        <v>85597</v>
       </c>
       <c r="B5" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -528,33 +528,33 @@
         <v>E</v>
       </c>
       <c r="D5" t="str">
-        <v>22/05/2026</v>
+        <v>07/07/2026</v>
       </c>
       <c r="E5" t="str">
-        <v>22/05/2026</v>
+        <v>24/06/2026</v>
       </c>
       <c r="F5" t="str">
-        <v>10/07/2026</v>
+        <v>20/07/2026</v>
       </c>
       <c r="G5" t="str">
-        <v>TYPHIMURIUM</v>
+        <v>LIVINGSTONE</v>
       </c>
       <c r="H5" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I5" t="str">
-        <v>MONTENERO DI BISACCIA</v>
+        <v>IRSINA</v>
       </c>
       <c r="J5" t="str">
-        <v>CB</v>
+        <v>MT</v>
       </c>
       <c r="K5" t="str">
-        <v>MOLISE</v>
+        <v>BASILICATA</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>83796</v>
+        <v>84625</v>
       </c>
       <c r="B6" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -563,33 +563,33 @@
         <v>E</v>
       </c>
       <c r="D6" t="str">
-        <v>20/03/2026</v>
+        <v>20/05/2026</v>
       </c>
       <c r="E6" t="str">
-        <v>10/03/2026</v>
+        <v>15/05/2026</v>
       </c>
       <c r="F6" t="str">
         <v>20/05/2026</v>
       </c>
       <c r="G6" t="str">
-        <v>TYPHIMURIUM</v>
+        <v>KENTUCKY</v>
       </c>
       <c r="H6" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I6" t="str">
-        <v>VILLACIDRO</v>
+        <v>MATERA</v>
       </c>
       <c r="J6" t="str">
-        <v>SU</v>
+        <v>MT</v>
       </c>
       <c r="K6" t="str">
-        <v>SARDEGNA</v>
+        <v>BASILICATA</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>83608</v>
+        <v>83784</v>
       </c>
       <c r="B7" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -598,33 +598,33 @@
         <v>E</v>
       </c>
       <c r="D7" t="str">
-        <v>05/03/2026</v>
+        <v>13/03/2026</v>
       </c>
       <c r="E7" t="str">
-        <v>05/03/2026</v>
+        <v>13/03/2026</v>
       </c>
       <c r="F7" t="str">
-        <v>24/04/2026</v>
+        <v>20/03/2026</v>
       </c>
       <c r="G7" t="str">
-        <v>ENTERITIDIS</v>
+        <v>TYPHIMURIUM</v>
       </c>
       <c r="H7" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I7" t="str">
-        <v>MONTALTO DI CASTRO</v>
+        <v>PARMA</v>
       </c>
       <c r="J7" t="str">
-        <v>VT</v>
+        <v>PR</v>
       </c>
       <c r="K7" t="str">
-        <v>LAZIO</v>
+        <v>EMILIA ROMAGNA</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>83232</v>
+        <v>84719</v>
       </c>
       <c r="B8" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -633,33 +633,33 @@
         <v>E</v>
       </c>
       <c r="D8" t="str">
-        <v>05/02/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="E8" t="str">
-        <v>27/01/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="F8" t="str">
-        <v>09/04/2026</v>
+        <v>10/07/2026</v>
       </c>
       <c r="G8" t="str">
-        <v>TYPHIMURIUM MONOFASICA VAR (1,4[5],12:I:-)</v>
+        <v>TYPHIMURIUM</v>
       </c>
       <c r="H8" t="str">
-        <v>TACCHINO</v>
+        <v>GALLUS GALLUS</v>
       </c>
       <c r="I8" t="str">
-        <v>SORGA\'</v>
+        <v>MONTENERO DI BISACCIA</v>
       </c>
       <c r="J8" t="str">
-        <v>VR</v>
+        <v>CB</v>
       </c>
       <c r="K8" t="str">
-        <v>VENETO</v>
+        <v>MOLISE</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>83301</v>
+        <v>83796</v>
       </c>
       <c r="B9" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -668,13 +668,13 @@
         <v>E</v>
       </c>
       <c r="D9" t="str">
-        <v>13/02/2026</v>
+        <v>20/03/2026</v>
       </c>
       <c r="E9" t="str">
-        <v>10/02/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="F9" t="str">
-        <v>23/03/2026</v>
+        <v>20/05/2026</v>
       </c>
       <c r="G9" t="str">
         <v>TYPHIMURIUM</v>
@@ -683,10 +683,10 @@
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I9" t="str">
-        <v>CHIARAMONTI</v>
+        <v>VILLACIDRO</v>
       </c>
       <c r="J9" t="str">
-        <v>SS</v>
+        <v>SU</v>
       </c>
       <c r="K9" t="str">
         <v>SARDEGNA</v>
@@ -694,7 +694,7 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>84163</v>
+        <v>83608</v>
       </c>
       <c r="B10" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -703,33 +703,33 @@
         <v>E</v>
       </c>
       <c r="D10" t="str">
-        <v>27/03/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="E10" t="str">
-        <v>27/03/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="F10" t="str">
-        <v>27/03/2026</v>
+        <v>24/04/2026</v>
       </c>
       <c r="G10" t="str">
-        <v>TYPHIMURIUM</v>
+        <v>ENTERITIDIS</v>
       </c>
       <c r="H10" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I10" t="str">
-        <v>LIMBADI</v>
+        <v>MONTALTO DI CASTRO</v>
       </c>
       <c r="J10" t="str">
-        <v>VV</v>
+        <v>VT</v>
       </c>
       <c r="K10" t="str">
-        <v>CALABRIA</v>
+        <v>LAZIO</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>84357</v>
+        <v>83232</v>
       </c>
       <c r="B11" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -738,33 +738,33 @@
         <v>E</v>
       </c>
       <c r="D11" t="str">
-        <v>20/04/2026</v>
+        <v>05/02/2026</v>
       </c>
       <c r="E11" t="str">
-        <v>26/03/2026</v>
+        <v>27/01/2026</v>
       </c>
       <c r="F11" t="str">
-        <v>28/05/2026</v>
+        <v>09/04/2026</v>
       </c>
       <c r="G11" t="str">
-        <v>ENTERITIDIS</v>
+        <v>TYPHIMURIUM MONOFASICA VAR (1,4[5],12:I:-)</v>
       </c>
       <c r="H11" t="str">
-        <v>GALLUS GALLUS</v>
+        <v>TACCHINO</v>
       </c>
       <c r="I11" t="str">
-        <v>COLICO</v>
+        <v>SORGA\'</v>
       </c>
       <c r="J11" t="str">
-        <v>LC</v>
+        <v>VR</v>
       </c>
       <c r="K11" t="str">
-        <v>LOMBARDIA</v>
+        <v>VENETO</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>83254</v>
+        <v>83301</v>
       </c>
       <c r="B12" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -773,33 +773,33 @@
         <v>E</v>
       </c>
       <c r="D12" t="str">
-        <v>04/02/2026</v>
+        <v>13/02/2026</v>
       </c>
       <c r="E12" t="str">
-        <v>04/02/2026</v>
+        <v>10/02/2026</v>
       </c>
       <c r="F12" t="str">
-        <v>10/02/2026</v>
+        <v>23/03/2026</v>
       </c>
       <c r="G12" t="str">
-        <v>UGANDA</v>
+        <v>TYPHIMURIUM</v>
       </c>
       <c r="H12" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I12" t="str">
-        <v>ORDONA</v>
+        <v>CHIARAMONTI</v>
       </c>
       <c r="J12" t="str">
-        <v>FG</v>
+        <v>SS</v>
       </c>
       <c r="K12" t="str">
-        <v>PUGLIA</v>
+        <v>SARDEGNA</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>83256</v>
+        <v>84163</v>
       </c>
       <c r="B13" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -808,33 +808,33 @@
         <v>E</v>
       </c>
       <c r="D13" t="str">
-        <v>05/02/2026</v>
+        <v>27/03/2026</v>
       </c>
       <c r="E13" t="str">
-        <v>29/01/2026</v>
+        <v>27/03/2026</v>
       </c>
       <c r="F13" t="str">
-        <v>29/05/2026</v>
+        <v>27/03/2026</v>
       </c>
       <c r="G13" t="str">
-        <v>ENTERITIDIS</v>
+        <v>TYPHIMURIUM</v>
       </c>
       <c r="H13" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I13" t="str">
-        <v>MONTECORVINO ROVELLA</v>
+        <v>LIMBADI</v>
       </c>
       <c r="J13" t="str">
-        <v>SA</v>
+        <v>VV</v>
       </c>
       <c r="K13" t="str">
-        <v>CAMPANIA</v>
+        <v>CALABRIA</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>85006</v>
+        <v>85600</v>
       </c>
       <c r="B14" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -843,33 +843,33 @@
         <v>E</v>
       </c>
       <c r="D14" t="str">
-        <v>26/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="E14" t="str">
-        <v>26/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="F14" t="str">
-        <v>23/06/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="G14" t="str">
-        <v>TYPHIMURIUM</v>
+        <v>KASENYI</v>
       </c>
       <c r="H14" t="str">
-        <v>QUAGLIA</v>
+        <v>GALLUS GALLUS</v>
       </c>
       <c r="I14" t="str">
-        <v>CARPI</v>
+        <v>IRSINA</v>
       </c>
       <c r="J14" t="str">
-        <v>MO</v>
+        <v>MT</v>
       </c>
       <c r="K14" t="str">
-        <v>EMILIA ROMAGNA</v>
+        <v>BASILICATA</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>84945</v>
+        <v>84357</v>
       </c>
       <c r="B15" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -878,13 +878,13 @@
         <v>E</v>
       </c>
       <c r="D15" t="str">
-        <v>29/05/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="E15" t="str">
-        <v>29/05/2026</v>
+        <v>26/03/2026</v>
       </c>
       <c r="F15" t="str">
-        <v>04/06/2026</v>
+        <v>28/05/2026</v>
       </c>
       <c r="G15" t="str">
         <v>ENTERITIDIS</v>
@@ -893,18 +893,18 @@
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I15" t="str">
-        <v>MONTIGLIO MONFERRATO</v>
+        <v>COLICO</v>
       </c>
       <c r="J15" t="str">
-        <v>AT</v>
+        <v>LC</v>
       </c>
       <c r="K15" t="str">
-        <v>PIEMONTE</v>
+        <v>LOMBARDIA</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>84058</v>
+        <v>84404</v>
       </c>
       <c r="B16" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -913,13 +913,13 @@
         <v>E</v>
       </c>
       <c r="D16" t="str">
-        <v>20/03/2026</v>
+        <v>27/04/2026</v>
       </c>
       <c r="E16" t="str">
-        <v>18/03/2026</v>
+        <v>15/04/2026</v>
       </c>
       <c r="F16" t="str">
-        <v>20/04/2026</v>
+        <v>10/06/2026</v>
       </c>
       <c r="G16" t="str">
         <v>TYPHIMURIUM</v>
@@ -928,18 +928,18 @@
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I16" t="str">
-        <v>URBISAGLIA</v>
+        <v>GRONTARDO</v>
       </c>
       <c r="J16" t="str">
-        <v>MC</v>
+        <v>CR</v>
       </c>
       <c r="K16" t="str">
-        <v>MARCHE</v>
+        <v>LOMBARDIA</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>85006</v>
+        <v>83254</v>
       </c>
       <c r="B17" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -948,33 +948,33 @@
         <v>E</v>
       </c>
       <c r="D17" t="str">
-        <v>26/05/2026</v>
+        <v>04/02/2026</v>
       </c>
       <c r="E17" t="str">
-        <v>26/05/2026</v>
+        <v>04/02/2026</v>
       </c>
       <c r="F17" t="str">
-        <v>23/06/2026</v>
+        <v>10/02/2026</v>
       </c>
       <c r="G17" t="str">
-        <v>TYPHIMURIUM</v>
+        <v>UGANDA</v>
       </c>
       <c r="H17" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I17" t="str">
-        <v>CARPI</v>
+        <v>ORDONA</v>
       </c>
       <c r="J17" t="str">
-        <v>MO</v>
+        <v>FG</v>
       </c>
       <c r="K17" t="str">
-        <v>EMILIA ROMAGNA</v>
+        <v>PUGLIA</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>83523</v>
+        <v>83256</v>
       </c>
       <c r="B18" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -983,33 +983,33 @@
         <v>E</v>
       </c>
       <c r="D18" t="str">
-        <v>25/02/2026</v>
+        <v>05/02/2026</v>
       </c>
       <c r="E18" t="str">
-        <v>25/02/2026</v>
+        <v>29/01/2026</v>
       </c>
       <c r="F18" t="str">
-        <v>08/04/2026</v>
+        <v>29/05/2026</v>
       </c>
       <c r="G18" t="str">
-        <v>TYPHIMURIUM</v>
+        <v>ENTERITIDIS</v>
       </c>
       <c r="H18" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I18" t="str">
-        <v>VILLA DEL CONTE</v>
+        <v>MONTECORVINO ROVELLA</v>
       </c>
       <c r="J18" t="str">
-        <v>PD</v>
+        <v>SA</v>
       </c>
       <c r="K18" t="str">
-        <v>VENETO</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>83780</v>
+        <v>85006</v>
       </c>
       <c r="B19" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1018,33 +1018,33 @@
         <v>E</v>
       </c>
       <c r="D19" t="str">
-        <v>19/03/2026</v>
+        <v>26/05/2026</v>
       </c>
       <c r="E19" t="str">
-        <v>17/03/2026</v>
+        <v>26/05/2026</v>
       </c>
       <c r="F19" t="str">
-        <v>20/04/2026</v>
+        <v>23/06/2026</v>
       </c>
       <c r="G19" t="str">
-        <v>TYPHIMURIUM MONOFASICA VAR (1,4[5],12:I:-)</v>
+        <v>TYPHIMURIUM</v>
       </c>
       <c r="H19" t="str">
-        <v>GALLUS GALLUS</v>
+        <v>QUAGLIA</v>
       </c>
       <c r="I19" t="str">
-        <v>TUSCANIA</v>
+        <v>CARPI</v>
       </c>
       <c r="J19" t="str">
-        <v>VT</v>
+        <v>MO</v>
       </c>
       <c r="K19" t="str">
-        <v>LAZIO</v>
+        <v>EMILIA ROMAGNA</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>83997</v>
+        <v>84945</v>
       </c>
       <c r="B20" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1053,173 +1053,173 @@
         <v>E</v>
       </c>
       <c r="D20" t="str">
-        <v>30/03/2026</v>
+        <v>29/05/2026</v>
       </c>
       <c r="E20" t="str">
-        <v>24/03/2026</v>
+        <v>29/05/2026</v>
       </c>
       <c r="F20" t="str">
-        <v>08/04/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="G20" t="str">
-        <v>KENTUCKY</v>
+        <v>ENTERITIDIS</v>
       </c>
       <c r="H20" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I20" t="str">
-        <v>MONTE SAN GIOVANNI CAMPANO</v>
+        <v>MONTIGLIO MONFERRATO</v>
       </c>
       <c r="J20" t="str">
-        <v>FR</v>
+        <v>AT</v>
       </c>
       <c r="K20" t="str">
-        <v>LAZIO</v>
+        <v>PIEMONTE</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>85416</v>
+        <v>83314</v>
       </c>
       <c r="B21" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C21" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D21" t="str">
-        <v>30/06/2026</v>
+        <v>05/02/2026</v>
       </c>
       <c r="E21" t="str">
-        <v>19/06/2026</v>
+        <v>29/01/2026</v>
       </c>
       <c r="F21" t="str">
-        <v>-</v>
+        <v>20/07/2026</v>
       </c>
       <c r="G21" t="str">
-        <v>TYPHIMURIUM</v>
+        <v>ENTERITIDIS</v>
       </c>
       <c r="H21" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I21" t="str">
-        <v>CASTELFRANCO VENETO</v>
+        <v>MONTECORVINO ROVELLA</v>
       </c>
       <c r="J21" t="str">
-        <v>TV</v>
+        <v>SA</v>
       </c>
       <c r="K21" t="str">
-        <v>VENETO</v>
+        <v>CAMPANIA</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>84068</v>
+        <v>84058</v>
       </c>
       <c r="B22" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C22" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D22" t="str">
-        <v>03/04/2026</v>
+        <v>20/03/2026</v>
       </c>
       <c r="E22" t="str">
-        <v>03/04/2026</v>
+        <v>18/03/2026</v>
       </c>
       <c r="F22" t="str">
-        <v>-</v>
+        <v>20/04/2026</v>
       </c>
       <c r="G22" t="str">
-        <v>TYPHIMURIUM MONOFASICA VAR (1,4[5],12:I:-)</v>
+        <v>TYPHIMURIUM</v>
       </c>
       <c r="H22" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I22" t="str">
-        <v>LIMBADI</v>
+        <v>URBISAGLIA</v>
       </c>
       <c r="J22" t="str">
-        <v>VV</v>
+        <v>MC</v>
       </c>
       <c r="K22" t="str">
-        <v>CALABRIA</v>
+        <v>MARCHE</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>83903</v>
+        <v>85006</v>
       </c>
       <c r="B23" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C23" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D23" t="str">
-        <v>25/03/2026</v>
+        <v>26/05/2026</v>
       </c>
       <c r="E23" t="str">
-        <v>17/03/2026</v>
+        <v>26/05/2026</v>
       </c>
       <c r="F23" t="str">
-        <v>-</v>
+        <v>23/06/2026</v>
       </c>
       <c r="G23" t="str">
-        <v>ENTERITIDIS</v>
+        <v>TYPHIMURIUM</v>
       </c>
       <c r="H23" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I23" t="str">
-        <v>ISOLA DELLA SCALA</v>
+        <v>CARPI</v>
       </c>
       <c r="J23" t="str">
-        <v>VR</v>
+        <v>MO</v>
       </c>
       <c r="K23" t="str">
-        <v>VENETO</v>
+        <v>EMILIA ROMAGNA</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>83314</v>
+        <v>83523</v>
       </c>
       <c r="B24" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C24" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D24" t="str">
-        <v>05/02/2026</v>
+        <v>25/02/2026</v>
       </c>
       <c r="E24" t="str">
-        <v>29/01/2026</v>
+        <v>25/02/2026</v>
       </c>
       <c r="F24" t="str">
-        <v>-</v>
+        <v>08/04/2026</v>
       </c>
       <c r="G24" t="str">
-        <v>ENTERITIDIS</v>
+        <v>TYPHIMURIUM</v>
       </c>
       <c r="H24" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I24" t="str">
-        <v>MONTECORVINO ROVELLA</v>
+        <v>VILLA DEL CONTE</v>
       </c>
       <c r="J24" t="str">
-        <v>SA</v>
+        <v>PD</v>
       </c>
       <c r="K24" t="str">
-        <v>CAMPANIA</v>
+        <v>VENETO</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>84404</v>
+        <v>85607</v>
       </c>
       <c r="B25" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1228,10 +1228,10 @@
         <v>C</v>
       </c>
       <c r="D25" t="str">
-        <v>27/04/2026</v>
+        <v>07/07/2026</v>
       </c>
       <c r="E25" t="str">
-        <v>15/04/2026</v>
+        <v>25/06/2026</v>
       </c>
       <c r="F25" t="str">
         <v>-</v>
@@ -1243,18 +1243,18 @@
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I25" t="str">
-        <v>GRONTARDO</v>
+        <v>CASTELFRANCO VENETO</v>
       </c>
       <c r="J25" t="str">
-        <v>CR</v>
+        <v>TV</v>
       </c>
       <c r="K25" t="str">
-        <v>LOMBARDIA</v>
+        <v>VENETO</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>84187</v>
+        <v>85638</v>
       </c>
       <c r="B26" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1263,28 +1263,28 @@
         <v>C</v>
       </c>
       <c r="D26" t="str">
-        <v>13/04/2026</v>
+        <v>13/07/2026</v>
       </c>
       <c r="E26" t="str">
-        <v>10/04/2026</v>
+        <v>13/07/2026</v>
       </c>
       <c r="F26" t="str">
         <v>-</v>
       </c>
       <c r="G26" t="str">
-        <v>ENTERITIDIS</v>
+        <v>TYPHIMURIUM</v>
       </c>
       <c r="H26" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I26" t="str">
-        <v>LONATO DEL GARDA</v>
+        <v>FORMIGINE</v>
       </c>
       <c r="J26" t="str">
-        <v>BS</v>
+        <v>MO</v>
       </c>
       <c r="K26" t="str">
-        <v>LOMBARDIA</v>
+        <v>EMILIA ROMAGNA</v>
       </c>
     </row>
     <row r="27">
@@ -1324,7 +1324,7 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>85558</v>
+        <v>84068</v>
       </c>
       <c r="B28" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1333,33 +1333,33 @@
         <v>C</v>
       </c>
       <c r="D28" t="str">
-        <v>07/07/2026</v>
+        <v>03/04/2026</v>
       </c>
       <c r="E28" t="str">
-        <v>02/07/2026</v>
+        <v>03/04/2026</v>
       </c>
       <c r="F28" t="str">
         <v>-</v>
       </c>
       <c r="G28" t="str">
-        <v>LIVINGSTONE</v>
+        <v>TYPHIMURIUM MONOFASICA VAR (1,4[5],12:I:-)</v>
       </c>
       <c r="H28" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I28" t="str">
-        <v>RICCIA</v>
+        <v>LIMBADI</v>
       </c>
       <c r="J28" t="str">
-        <v>CB</v>
+        <v>VV</v>
       </c>
       <c r="K28" t="str">
-        <v>MOLISE</v>
+        <v>CALABRIA</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>83804</v>
+        <v>85705</v>
       </c>
       <c r="B29" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1368,33 +1368,33 @@
         <v>C</v>
       </c>
       <c r="D29" t="str">
-        <v>18/03/2026</v>
+        <v>20/07/2026</v>
       </c>
       <c r="E29" t="str">
-        <v>17/03/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="F29" t="str">
         <v>-</v>
       </c>
       <c r="G29" t="str">
-        <v>ENTERITIDIS</v>
+        <v>Sconosciuto</v>
       </c>
       <c r="H29" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I29" t="str">
-        <v>TAGLIO DI PO</v>
+        <v>CELLENO</v>
       </c>
       <c r="J29" t="str">
-        <v>RO</v>
+        <v>VT</v>
       </c>
       <c r="K29" t="str">
-        <v>VENETO</v>
+        <v>LAZIO</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>85001</v>
+        <v>85679</v>
       </c>
       <c r="B30" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1403,33 +1403,33 @@
         <v>C</v>
       </c>
       <c r="D30" t="str">
-        <v>05/06/2026</v>
+        <v>16/07/2026</v>
       </c>
       <c r="E30" t="str">
-        <v>05/06/2026</v>
+        <v>07/07/2026</v>
       </c>
       <c r="F30" t="str">
         <v>-</v>
       </c>
       <c r="G30" t="str">
-        <v>TYPHIMURIUM</v>
+        <v>ENTERITIDIS</v>
       </c>
       <c r="H30" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I30" t="str">
-        <v>RODENGO-SAIANO</v>
+        <v>ISOLA DELLA SCALA</v>
       </c>
       <c r="J30" t="str">
-        <v>BS</v>
+        <v>VR</v>
       </c>
       <c r="K30" t="str">
-        <v>LOMBARDIA</v>
+        <v>VENETO</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>85317</v>
+        <v>83903</v>
       </c>
       <c r="B31" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1438,33 +1438,33 @@
         <v>C</v>
       </c>
       <c r="D31" t="str">
-        <v>24/06/2026</v>
+        <v>25/03/2026</v>
       </c>
       <c r="E31" t="str">
-        <v>24/06/2026</v>
+        <v>17/03/2026</v>
       </c>
       <c r="F31" t="str">
         <v>-</v>
       </c>
       <c r="G31" t="str">
-        <v>TYPHIMURIUM</v>
+        <v>ENTERITIDIS</v>
       </c>
       <c r="H31" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I31" t="str">
-        <v>CURTATONE</v>
+        <v>ISOLA DELLA SCALA</v>
       </c>
       <c r="J31" t="str">
-        <v>MN</v>
+        <v>VR</v>
       </c>
       <c r="K31" t="str">
-        <v>LOMBARDIA</v>
+        <v>VENETO</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>85267</v>
+        <v>84187</v>
       </c>
       <c r="B32" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1473,33 +1473,33 @@
         <v>C</v>
       </c>
       <c r="D32" t="str">
-        <v>23/06/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="E32" t="str">
-        <v>23/06/2026</v>
+        <v>10/04/2026</v>
       </c>
       <c r="F32" t="str">
         <v>-</v>
       </c>
       <c r="G32" t="str">
-        <v>INFANTIS</v>
+        <v>ENTERITIDIS</v>
       </c>
       <c r="H32" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I32" t="str">
-        <v>CAPRINO VERONESE</v>
+        <v>LONATO DEL GARDA</v>
       </c>
       <c r="J32" t="str">
-        <v>VR</v>
+        <v>BS</v>
       </c>
       <c r="K32" t="str">
-        <v>VENETO</v>
+        <v>LOMBARDIA</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>85238</v>
+        <v>83804</v>
       </c>
       <c r="B33" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1508,25 +1508,25 @@
         <v>C</v>
       </c>
       <c r="D33" t="str">
-        <v>12/06/2026</v>
+        <v>18/03/2026</v>
       </c>
       <c r="E33" t="str">
-        <v>11/06/2026</v>
+        <v>17/03/2026</v>
       </c>
       <c r="F33" t="str">
         <v>-</v>
       </c>
       <c r="G33" t="str">
-        <v>TYPHIMURIUM</v>
+        <v>ENTERITIDIS</v>
       </c>
       <c r="H33" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I33" t="str">
-        <v>PIEVE DEL GRAPPA</v>
+        <v>TAGLIO DI PO</v>
       </c>
       <c r="J33" t="str">
-        <v>TV</v>
+        <v>RO</v>
       </c>
       <c r="K33" t="str">
         <v>VENETO</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>85266</v>
+        <v>85558</v>
       </c>
       <c r="B34" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1543,33 +1543,33 @@
         <v>C</v>
       </c>
       <c r="D34" t="str">
-        <v>29/06/2026</v>
+        <v>07/07/2026</v>
       </c>
       <c r="E34" t="str">
-        <v>22/06/2026</v>
+        <v>02/07/2026</v>
       </c>
       <c r="F34" t="str">
         <v>-</v>
       </c>
       <c r="G34" t="str">
-        <v>TYPHIMURIUM</v>
+        <v>LIVINGSTONE</v>
       </c>
       <c r="H34" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I34" t="str">
-        <v>CIGOLE</v>
+        <v>RICCIA</v>
       </c>
       <c r="J34" t="str">
-        <v>BS</v>
+        <v>CB</v>
       </c>
       <c r="K34" t="str">
-        <v>LOMBARDIA</v>
+        <v>MOLISE</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>83388</v>
+        <v>85001</v>
       </c>
       <c r="B35" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1578,33 +1578,33 @@
         <v>C</v>
       </c>
       <c r="D35" t="str">
-        <v>19/02/2026</v>
+        <v>05/06/2026</v>
       </c>
       <c r="E35" t="str">
-        <v>10/02/2026</v>
+        <v>05/06/2026</v>
       </c>
       <c r="F35" t="str">
         <v>-</v>
       </c>
       <c r="G35" t="str">
-        <v>ENTERITIDIS</v>
+        <v>TYPHIMURIUM</v>
       </c>
       <c r="H35" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I35" t="str">
-        <v>PRESSANA</v>
+        <v>RODENGO-SAIANO</v>
       </c>
       <c r="J35" t="str">
-        <v>VR</v>
+        <v>BS</v>
       </c>
       <c r="K35" t="str">
-        <v>VENETO</v>
+        <v>LOMBARDIA</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>85062</v>
+        <v>85416</v>
       </c>
       <c r="B36" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -1613,22 +1613,22 @@
         <v>C</v>
       </c>
       <c r="D36" t="str">
-        <v>12/06/2026</v>
+        <v>30/06/2026</v>
       </c>
       <c r="E36" t="str">
-        <v>12/06/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="F36" t="str">
         <v>-</v>
       </c>
       <c r="G36" t="str">
-        <v>TYPHIMURIUM MONOFASICA VAR (1,4[5],12:I:-)</v>
+        <v>TYPHIMURIUM</v>
       </c>
       <c r="H36" t="str">
         <v>GALLUS GALLUS</v>
       </c>
       <c r="I36" t="str">
-        <v>PIEVE DEL GRAPPA</v>
+        <v>CASTELFRANCO VENETO</v>
       </c>
       <c r="J36" t="str">
         <v>TV</v>
@@ -1637,9 +1637,254 @@
         <v>VENETO</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37">
+        <v>85317</v>
+      </c>
+      <c r="B37" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C37" t="str">
+        <v>C</v>
+      </c>
+      <c r="D37" t="str">
+        <v>24/06/2026</v>
+      </c>
+      <c r="E37" t="str">
+        <v>24/06/2026</v>
+      </c>
+      <c r="F37" t="str">
+        <v>-</v>
+      </c>
+      <c r="G37" t="str">
+        <v>TYPHIMURIUM</v>
+      </c>
+      <c r="H37" t="str">
+        <v>GALLUS GALLUS</v>
+      </c>
+      <c r="I37" t="str">
+        <v>CURTATONE</v>
+      </c>
+      <c r="J37" t="str">
+        <v>MN</v>
+      </c>
+      <c r="K37" t="str">
+        <v>LOMBARDIA</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>85267</v>
+      </c>
+      <c r="B38" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C38" t="str">
+        <v>C</v>
+      </c>
+      <c r="D38" t="str">
+        <v>23/06/2026</v>
+      </c>
+      <c r="E38" t="str">
+        <v>23/06/2026</v>
+      </c>
+      <c r="F38" t="str">
+        <v>-</v>
+      </c>
+      <c r="G38" t="str">
+        <v>INFANTIS</v>
+      </c>
+      <c r="H38" t="str">
+        <v>GALLUS GALLUS</v>
+      </c>
+      <c r="I38" t="str">
+        <v>CAPRINO VERONESE</v>
+      </c>
+      <c r="J38" t="str">
+        <v>VR</v>
+      </c>
+      <c r="K38" t="str">
+        <v>VENETO</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>85651</v>
+      </c>
+      <c r="B39" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C39" t="str">
+        <v>C</v>
+      </c>
+      <c r="D39" t="str">
+        <v>23/07/2026</v>
+      </c>
+      <c r="E39" t="str">
+        <v>16/07/2026</v>
+      </c>
+      <c r="F39" t="str">
+        <v>-</v>
+      </c>
+      <c r="G39" t="str">
+        <v>COELN</v>
+      </c>
+      <c r="H39" t="str">
+        <v>GALLUS GALLUS</v>
+      </c>
+      <c r="I39" t="str">
+        <v>OLEVANO SUL TUSCIANO</v>
+      </c>
+      <c r="J39" t="str">
+        <v>SA</v>
+      </c>
+      <c r="K39" t="str">
+        <v>CAMPANIA</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>85238</v>
+      </c>
+      <c r="B40" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C40" t="str">
+        <v>C</v>
+      </c>
+      <c r="D40" t="str">
+        <v>12/06/2026</v>
+      </c>
+      <c r="E40" t="str">
+        <v>11/06/2026</v>
+      </c>
+      <c r="F40" t="str">
+        <v>-</v>
+      </c>
+      <c r="G40" t="str">
+        <v>TYPHIMURIUM</v>
+      </c>
+      <c r="H40" t="str">
+        <v>GALLUS GALLUS</v>
+      </c>
+      <c r="I40" t="str">
+        <v>PIEVE DEL GRAPPA</v>
+      </c>
+      <c r="J40" t="str">
+        <v>TV</v>
+      </c>
+      <c r="K40" t="str">
+        <v>VENETO</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>85266</v>
+      </c>
+      <c r="B41" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C41" t="str">
+        <v>C</v>
+      </c>
+      <c r="D41" t="str">
+        <v>29/06/2026</v>
+      </c>
+      <c r="E41" t="str">
+        <v>22/06/2026</v>
+      </c>
+      <c r="F41" t="str">
+        <v>-</v>
+      </c>
+      <c r="G41" t="str">
+        <v>TYPHIMURIUM</v>
+      </c>
+      <c r="H41" t="str">
+        <v>GALLUS GALLUS</v>
+      </c>
+      <c r="I41" t="str">
+        <v>CIGOLE</v>
+      </c>
+      <c r="J41" t="str">
+        <v>BS</v>
+      </c>
+      <c r="K41" t="str">
+        <v>LOMBARDIA</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>83388</v>
+      </c>
+      <c r="B42" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C42" t="str">
+        <v>C</v>
+      </c>
+      <c r="D42" t="str">
+        <v>19/02/2026</v>
+      </c>
+      <c r="E42" t="str">
+        <v>10/02/2026</v>
+      </c>
+      <c r="F42" t="str">
+        <v>-</v>
+      </c>
+      <c r="G42" t="str">
+        <v>ENTERITIDIS</v>
+      </c>
+      <c r="H42" t="str">
+        <v>GALLUS GALLUS</v>
+      </c>
+      <c r="I42" t="str">
+        <v>PRESSANA</v>
+      </c>
+      <c r="J42" t="str">
+        <v>VR</v>
+      </c>
+      <c r="K42" t="str">
+        <v>VENETO</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>85062</v>
+      </c>
+      <c r="B43" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C43" t="str">
+        <v>C</v>
+      </c>
+      <c r="D43" t="str">
+        <v>12/06/2026</v>
+      </c>
+      <c r="E43" t="str">
+        <v>12/06/2026</v>
+      </c>
+      <c r="F43" t="str">
+        <v>-</v>
+      </c>
+      <c r="G43" t="str">
+        <v>TYPHIMURIUM MONOFASICA VAR (1,4[5],12:I:-)</v>
+      </c>
+      <c r="H43" t="str">
+        <v>GALLUS GALLUS</v>
+      </c>
+      <c r="I43" t="str">
+        <v>PIEVE DEL GRAPPA</v>
+      </c>
+      <c r="J43" t="str">
+        <v>TV</v>
+      </c>
+      <c r="K43" t="str">
+        <v>VENETO</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K43"/>
   </ignoredErrors>
 </worksheet>
 </file>